--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/guild_doorman.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/guild_doorman.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" r:id="rId3"/>
+    <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="103">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -335,96 +335,6 @@
   </si>
   <si>
     <t xml:space="preserve">$chill</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯？你带推荐信来了？让我看看。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯，确实是学院的推荐信没错。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看来你已经接触过让黑暗成为同伴的技巧了。合格了…。从今天开始你就是盗贼公会的一员了。以后要遵守公会的规则，完成自己的定额任务。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">恭喜你…合格了。从今天开始你成为了魔法师公会的一员。以后要遵守公会的规则，完成自己的定额任务。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">恭喜你…合格了。从今天开始你成为了战士公会的一员。以后要遵守公会的规则，完成自己的定额任务。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎来到盗贼公会，#guild_title #pc…请进。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎来到魔法师公会，#guild_title #pc…请进。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎来到战士公会，#guild_title #pc…请进。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">停下…。走过这扇门就是盗贼公会的管辖区域。公会成员以外的人不能进入…。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">止步…。走过这扇门就是魔法师公会的管辖区域。公会成员以外的人不能进入…。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">止步…。走过这扇门就是战士公会的管辖区域。公会成员以外的人不能进入…。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">盗贼公会是？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">魔法师公会是？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">战士公会是？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我想加入盗贼公会</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我想加入魔法师公会</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我想加入战士公会</t>
-  </si>
-  <si>
-    <t xml:space="preserve">盗贼公会「夜之白布」是管辖各地盗贼的组织…。公会成员需要遵守纪律以及完成定额任务，相对的，公会会为你提供援助，介绍特定的工作。
-盗贼公会的成员可以享有高价出售赃物、在黑市打折、学习和训练盗贼技能等福利。不过想要加入公会，必须经过严格的审查。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">魔法师公会是管辖各地魔法师的公会。公会成员需要遵守纪律以及完成定额任务，相对的，公会会为你提供援助，介绍特定的工作。
-魔法师公会的成员可以享有预定魔法书、在所有店铺购买魔法书时获得折扣、学习和训练魔法技能等福利。不过想要加入公会，必须经过严格的审查。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">战士公会是管辖各地战士的公会。公会成员需要遵守纪律以及完成定额任务，相对的，公会会为你提供援助，介绍特定的工作。
-战士公会的成员可以享有鉴定价格打折、能力复原价格打折、学习和训练战士技能等福利。不过想要加入公会，必须经过严格的审查。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">想加入盗贼公会…？正如我们被世人认知那样，我们置身于黑暗的世界。想加入我们首先得让我试试你是否值得信赖。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你是想加入魔法师公会吗……我们的学院不问出身，欢迎所有追求知识的人。不过我得审查一下你适不适合成为我们的一份子。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">想加入战士公会么…我们需要的是不畏惧任何强敌，能切实完成被赋予指令的真正猎人。让我试试你的本事如何吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好的</t>
-  </si>
-  <si>
-    <t xml:space="preserve">算了</t>
-  </si>
-  <si>
-    <t xml:space="preserve">盗贼公会的考试很简单。想进入「夜之白布」的人，只要违背「他们」制定的法律，积累罪案就可以了。和束缚你的愚蠢道德和习惯诀别，进入把自己染上阴影的世界。当然，「他们」会驱逐你。你的伙伴只有自己的力量和黑暗。当你能于夜幕中安然自得的生活之后，再来找我吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">说是审查，也没有那么麻烦。只要提交魔法师公会成员的推荐信就可以了。如果没有收到推荐信机会的缘分，也可以去店里买……我个人是不喜欢这样的，不过这是公会会长的意思…。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那就给你入团考试吧。战士公会接到最多的委托就是驱除那些喜欢恶作剧的小鬼。公会里那些熟练的战士们已经处理小鬼处理到头疼了。不如这样，你先去试着讨伐20只小鬼。能做到吗？</t>
   </si>
 </sst>
 </file>
@@ -446,25 +356,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -483,7 +393,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -492,62 +402,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -561,13 +471,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -743,25 +653,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L66"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" width="8.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.56" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.36" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.85" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
-    <col min="10" max="10" width="42.14" style="1" customWidth="1"/>
-    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="23.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="42.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -799,30 +709,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="I2" s="1">
-        <f>MAX(I4:I1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
         <v>33</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="1" t="n">
         <v>32</v>
       </c>
       <c r="J9" s="1" t="s">
@@ -831,15 +741,12 @@
       <c r="K9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" ht="12.8">
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="1" t="n">
         <v>33</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -848,11 +755,8 @@
       <c r="K10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" ht="12.8">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
@@ -863,7 +767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
@@ -871,7 +775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" ht="12.8">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="2" t="s">
         <v>23</v>
       </c>
@@ -882,14 +786,14 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" ht="43.25">
+    <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="1" t="n">
         <v>29</v>
       </c>
       <c r="J15" s="4" t="s">
@@ -898,18 +802,15 @@
       <c r="K15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" ht="32.8">
+    </row>
+    <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="1" t="n">
         <v>30</v>
       </c>
       <c r="J16" s="5" t="s">
@@ -918,18 +819,15 @@
       <c r="K16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L16" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="17" ht="32.8">
+    </row>
+    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="1" t="n">
         <v>31</v>
       </c>
       <c r="J17" s="4" t="s">
@@ -938,11 +836,8 @@
       <c r="K17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" ht="12.8">
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="2" t="s">
         <v>23</v>
       </c>
@@ -951,17 +846,17 @@
       </c>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J19" s="4"/>
     </row>
-    <row r="20" ht="22.35">
+    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="1" t="n">
         <v>26</v>
       </c>
       <c r="J20" s="4" t="s">
@@ -970,18 +865,15 @@
       <c r="K20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L20" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" ht="22.35">
+    </row>
+    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="1" t="n">
         <v>27</v>
       </c>
       <c r="J21" s="5" t="s">
@@ -990,18 +882,15 @@
       <c r="K21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" ht="22.35">
+    </row>
+    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="1" t="n">
         <v>28</v>
       </c>
       <c r="J22" s="4" t="s">
@@ -1010,21 +899,18 @@
       <c r="K22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" ht="12.8">
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J23" s="4"/>
     </row>
-    <row r="24" ht="32.8">
+    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="4" t="s">
@@ -1033,18 +919,15 @@
       <c r="K24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L24" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" ht="32.8">
+    </row>
+    <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J25" s="5" t="s">
@@ -1053,18 +936,15 @@
       <c r="K25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L25" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" ht="32.8">
+    </row>
+    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I26" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J26" s="4" t="s">
@@ -1073,14 +953,11 @@
       <c r="K26" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" ht="12.8">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J27" s="4"/>
     </row>
-    <row r="28" ht="12.8">
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
         <v>54</v>
       </c>
@@ -1090,7 +967,7 @@
       <c r="E28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I28" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J28" s="4" t="s">
@@ -1099,11 +976,8 @@
       <c r="K28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="L28" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="29" ht="12.8">
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
         <v>54</v>
       </c>
@@ -1113,7 +987,7 @@
       <c r="E29" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I29" s="1" t="n">
         <v>21</v>
       </c>
       <c r="J29" s="5" t="s">
@@ -1122,11 +996,8 @@
       <c r="K29" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L29" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="30" ht="12.8">
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="s">
         <v>54</v>
       </c>
@@ -1136,7 +1007,7 @@
       <c r="E30" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30" s="1" t="n">
         <v>22</v>
       </c>
       <c r="J30" s="4" t="s">
@@ -1145,11 +1016,8 @@
       <c r="K30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L30" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="31" ht="12.8">
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
         <v>62</v>
       </c>
@@ -1162,7 +1030,7 @@
       <c r="E31" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I31" s="1">
+      <c r="I31" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J31" s="4" t="s">
@@ -1171,11 +1039,8 @@
       <c r="K31" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="L31" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" ht="12.8">
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="1" t="s">
         <v>62</v>
       </c>
@@ -1188,7 +1053,7 @@
       <c r="E32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I32" s="1">
+      <c r="I32" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J32" s="4" t="s">
@@ -1197,11 +1062,8 @@
       <c r="K32" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L32" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" ht="12.8">
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="1" t="s">
         <v>62</v>
       </c>
@@ -1214,7 +1076,7 @@
       <c r="E33" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I33" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J33" s="4" t="s">
@@ -1223,11 +1085,8 @@
       <c r="K33" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="L33" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" ht="12.8">
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E34" s="1" t="s">
         <v>72</v>
       </c>
@@ -1236,38 +1095,38 @@
       </c>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" ht="12.8">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E35" s="1" t="s">
         <v>74</v>
       </c>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E36" s="1" t="s">
         <v>75</v>
       </c>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" ht="12.8">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J37" s="4"/>
     </row>
-    <row r="38" ht="12.8">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J38" s="4"/>
     </row>
-    <row r="39" ht="12.8">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>54</v>
       </c>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" ht="12.8">
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J40" s="4"/>
     </row>
-    <row r="41" ht="95.5">
+    <row r="41" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C41" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I41" s="1">
+      <c r="I41" s="1" t="n">
         <v>17</v>
       </c>
       <c r="J41" s="4" t="s">
@@ -1276,15 +1135,12 @@
       <c r="K41" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="L41" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="42" ht="95.5">
+    </row>
+    <row r="42" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C42" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I42" s="1">
+      <c r="I42" s="1" t="n">
         <v>18</v>
       </c>
       <c r="J42" s="4" t="s">
@@ -1293,15 +1149,12 @@
       <c r="K42" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="L42" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="43" ht="85.05">
+    </row>
+    <row r="43" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C43" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="1">
+      <c r="I43" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J43" s="4" t="s">
@@ -1310,36 +1163,33 @@
       <c r="K43" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="L43" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="44" ht="12.8">
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="1" t="s">
         <v>82</v>
       </c>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" ht="12.8">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J45" s="4"/>
     </row>
-    <row r="46" ht="12.8">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J46" s="4"/>
     </row>
-    <row r="47" ht="12.8">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>62</v>
       </c>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" ht="12.8">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J48" s="4"/>
     </row>
-    <row r="49" ht="43.25">
+    <row r="49" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C49" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I49" s="1">
+      <c r="I49" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J49" s="4" t="s">
@@ -1348,15 +1198,12 @@
       <c r="K49" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="L49" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="50" ht="53.7">
+    </row>
+    <row r="50" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C50" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I50" s="1">
+      <c r="I50" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J50" s="5" t="s">
@@ -1365,15 +1212,12 @@
       <c r="K50" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L50" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="51" ht="43.25">
+    </row>
+    <row r="51" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C51" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="1">
+      <c r="I51" s="1" t="n">
         <v>9</v>
       </c>
       <c r="J51" s="4" t="s">
@@ -1382,21 +1226,18 @@
       <c r="K51" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L51" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="52" ht="12.8">
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J52" s="4"/>
     </row>
-    <row r="53" ht="12.8">
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="1" t="s">
         <v>89</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I53" s="1">
+      <c r="I53" s="1" t="n">
         <v>12</v>
       </c>
       <c r="J53" s="4" t="s">
@@ -1405,18 +1246,15 @@
       <c r="K53" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="L53" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="54" ht="12.8">
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I54" s="1">
+      <c r="I54" s="1" t="n">
         <v>13</v>
       </c>
       <c r="J54" s="4" t="s">
@@ -1425,11 +1263,8 @@
       <c r="K54" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="L54" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="55" ht="12.8">
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="1" t="s">
         <v>92</v>
       </c>
@@ -1438,20 +1273,20 @@
       </c>
       <c r="J55" s="4"/>
     </row>
-    <row r="56" ht="12.8">
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J56" s="4"/>
     </row>
-    <row r="57" ht="12.8">
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>89</v>
       </c>
       <c r="J57" s="4"/>
     </row>
-    <row r="58" ht="91">
+    <row r="58" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C58" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I58" s="1">
+      <c r="I58" s="1" t="n">
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
@@ -1460,15 +1295,12 @@
       <c r="K58" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="L58" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="59" ht="53.7">
+    </row>
+    <row r="59" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C59" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I59" s="1">
+      <c r="I59" s="1" t="n">
         <v>24</v>
       </c>
       <c r="J59" s="5" t="s">
@@ -1477,15 +1309,12 @@
       <c r="K59" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L59" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="60" ht="64.15">
+    </row>
+    <row r="60" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C60" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I60" s="1">
+      <c r="I60" s="1" t="n">
         <v>25</v>
       </c>
       <c r="J60" s="4" t="s">
@@ -1494,11 +1323,8 @@
       <c r="K60" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="L60" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="61" ht="12.8">
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E61" s="1" t="s">
         <v>20</v>
       </c>
@@ -1507,25 +1333,25 @@
       </c>
       <c r="J61" s="4"/>
     </row>
-    <row r="62" ht="12.8">
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E62" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J62" s="4"/>
     </row>
-    <row r="63" ht="12.8">
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J63" s="4"/>
     </row>
-    <row r="64" ht="12.8">
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="65" ht="12.8">
-      <c r="I65" s="1">
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I65" s="1" t="n">
         <v>15</v>
       </c>
       <c r="J65" s="1" t="s">
@@ -1534,23 +1360,20 @@
       <c r="K65" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="L65" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="66" ht="12.8">
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="1" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/guild_doorman.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/guild_doorman.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="132">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -335,6 +335,96 @@
   </si>
   <si>
     <t xml:space="preserve">$chill</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯？你带推荐信来了？让我看看。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯，确实是学院的推荐信没错。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看来你已经接触过让黑暗成为同伴的技巧了。合格了…。从今天开始你就是盗贼公会的一员了。以后要遵守公会的规则，完成自己的定额任务。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">恭喜你…合格了。从今天开始你成为了魔法师公会的一员。以后要遵守公会的规则，完成自己的定额任务。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">恭喜你…合格了。从今天开始你成为了战士公会的一员。以后要遵守公会的规则，完成自己的定额任务。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欢迎来到盗贼公会，#guild_title #pc…请进。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欢迎来到魔法师公会，#guild_title #pc…请进。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欢迎来到战士公会，#guild_title #pc…请进。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">停下…。走过这扇门就是盗贼公会的管辖区域。公会成员以外的人不能进入…。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">止步…。走过这扇门就是魔法师公会的管辖区域。公会成员以外的人不能进入…。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">止步…。走过这扇门就是战士公会的管辖区域。公会成员以外的人不能进入…。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">盗贼公会是？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">魔法师公会是？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">战士公会是？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我想加入盗贼公会</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我想加入魔法师公会</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我想加入战士公会</t>
+  </si>
+  <si>
+    <t xml:space="preserve">盗贼公会「夜之白布」是管辖各地盗贼的组织…。公会成员需要遵守纪律以及完成定额任务，相对的，公会会为你提供援助，介绍特定的工作。
+盗贼公会的成员可以享有高价出售赃物、在黑市打折、学习和训练盗贼技能等福利。不过想要加入公会，必须经过严格的审查。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">魔法师公会是管辖各地魔法师的公会。公会成员需要遵守纪律以及完成定额任务，相对的，公会会为你提供援助，介绍特定的工作。
+魔法师公会的成员可以享有预定魔法书、在所有店铺购买魔法书时获得折扣、学习和训练魔法技能等福利。不过想要加入公会，必须经过严格的审查。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">战士公会是管辖各地战士的公会。公会成员需要遵守纪律以及完成定额任务，相对的，公会会为你提供援助，介绍特定的工作。
+战士公会的成员可以享有鉴定价格打折、能力复原价格打折、学习和训练战士技能等福利。不过想要加入公会，必须经过严格的审查。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">想加入盗贼公会…？正如我们被世人认知那样，我们置身于黑暗的世界。想加入我们首先得让我试试你是否值得信赖。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你是想加入魔法师公会吗……我们的学院不问出身，欢迎所有追求知识的人。不过我得审查一下你适不适合成为我们的一份子。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">想加入战士公会么…我们需要的是不畏惧任何强敌，能切实完成被赋予指令的真正猎人。让我试试你的本事如何吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">算了</t>
+  </si>
+  <si>
+    <t xml:space="preserve">盗贼公会的考试很简单。想进入「夜之白布」的人，只要违背「他们」制定的法律，积累罪案就可以了。和束缚你的愚蠢道德和习惯诀别，进入把自己染上阴影的世界。当然，「他们」会驱逐你。你的伙伴只有自己的力量和黑暗。当你能于夜幕中安然自得的生活之后，再来找我吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">说是审查，也没有那么麻烦。只要提交魔法师公会成员的推荐信就可以了。如果没有收到推荐信机会的缘分，也可以去店里买……我个人是不喜欢这样的，不过这是公会会长的意思…。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那就给你入团考试吧。战士公会接到最多的委托就是驱除那些喜欢恶作剧的小鬼。公会里那些熟练的战士们已经处理小鬼处理到头疼了。不如这样，你先去试着讨伐20只小鬼。能做到吗？</t>
   </si>
 </sst>
 </file>
@@ -356,25 +446,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -393,7 +483,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -402,62 +492,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -471,13 +561,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -653,25 +743,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L66"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="23.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="42.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
+    <col min="1" max="2" width="8.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.56" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.36" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="42.14" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -709,30 +799,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.8">
       <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="I9" s="1">
         <v>32</v>
       </c>
       <c r="J9" s="1" t="s">
@@ -741,12 +831,15 @@
       <c r="K9" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" ht="12.8">
       <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="1">
         <v>33</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -755,8 +848,11 @@
       <c r="K10" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" ht="12.8">
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
@@ -767,7 +863,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
@@ -775,7 +871,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="12.8">
       <c r="D14" s="2" t="s">
         <v>23</v>
       </c>
@@ -786,14 +882,14 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="43.25">
       <c r="C15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="1" t="n">
+      <c r="I15" s="1">
         <v>29</v>
       </c>
       <c r="J15" s="4" t="s">
@@ -802,15 +898,18 @@
       <c r="K15" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" ht="32.8">
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="1" t="n">
+      <c r="I16" s="1">
         <v>30</v>
       </c>
       <c r="J16" s="5" t="s">
@@ -819,15 +918,18 @@
       <c r="K16" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" ht="32.8">
       <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="I17" s="1">
         <v>31</v>
       </c>
       <c r="J17" s="4" t="s">
@@ -836,8 +938,11 @@
       <c r="K17" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" ht="12.8">
       <c r="D18" s="2" t="s">
         <v>23</v>
       </c>
@@ -846,17 +951,17 @@
       </c>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.8">
       <c r="J19" s="4"/>
     </row>
-    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="22.35">
       <c r="C20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I20" s="1" t="n">
+      <c r="I20" s="1">
         <v>26</v>
       </c>
       <c r="J20" s="4" t="s">
@@ -865,15 +970,18 @@
       <c r="K20" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" ht="22.35">
       <c r="C21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I21" s="1" t="n">
+      <c r="I21" s="1">
         <v>27</v>
       </c>
       <c r="J21" s="5" t="s">
@@ -882,15 +990,18 @@
       <c r="K21" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" ht="22.35">
       <c r="C22" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I22" s="1" t="n">
+      <c r="I22" s="1">
         <v>28</v>
       </c>
       <c r="J22" s="4" t="s">
@@ -899,18 +1010,21 @@
       <c r="K22" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" ht="12.8">
       <c r="J23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="32.8">
       <c r="C24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I24" s="1" t="n">
+      <c r="I24" s="1">
         <v>1</v>
       </c>
       <c r="J24" s="4" t="s">
@@ -919,15 +1033,18 @@
       <c r="K24" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L24" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" ht="32.8">
       <c r="C25" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I25" s="1" t="n">
+      <c r="I25" s="1">
         <v>2</v>
       </c>
       <c r="J25" s="5" t="s">
@@ -936,15 +1053,18 @@
       <c r="K25" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" ht="32.8">
       <c r="C26" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="1" t="n">
+      <c r="I26" s="1">
         <v>3</v>
       </c>
       <c r="J26" s="4" t="s">
@@ -953,11 +1073,14 @@
       <c r="K26" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" ht="12.8">
       <c r="J27" s="4"/>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="12.8">
       <c r="B28" s="1" t="s">
         <v>54</v>
       </c>
@@ -967,7 +1090,7 @@
       <c r="E28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I28" s="1" t="n">
+      <c r="I28" s="1">
         <v>20</v>
       </c>
       <c r="J28" s="4" t="s">
@@ -976,8 +1099,11 @@
       <c r="K28" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" ht="12.8">
       <c r="B29" s="1" t="s">
         <v>54</v>
       </c>
@@ -987,7 +1113,7 @@
       <c r="E29" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I29" s="1" t="n">
+      <c r="I29" s="1">
         <v>21</v>
       </c>
       <c r="J29" s="5" t="s">
@@ -996,8 +1122,11 @@
       <c r="K29" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L29" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" ht="12.8">
       <c r="B30" s="1" t="s">
         <v>54</v>
       </c>
@@ -1007,7 +1136,7 @@
       <c r="E30" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I30" s="1" t="n">
+      <c r="I30" s="1">
         <v>22</v>
       </c>
       <c r="J30" s="4" t="s">
@@ -1016,8 +1145,11 @@
       <c r="K30" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" ht="12.8">
       <c r="B31" s="1" t="s">
         <v>62</v>
       </c>
@@ -1030,7 +1162,7 @@
       <c r="E31" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I31" s="1" t="n">
+      <c r="I31" s="1">
         <v>4</v>
       </c>
       <c r="J31" s="4" t="s">
@@ -1039,8 +1171,11 @@
       <c r="K31" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" ht="12.8">
       <c r="B32" s="1" t="s">
         <v>62</v>
       </c>
@@ -1053,7 +1188,7 @@
       <c r="E32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I32" s="1" t="n">
+      <c r="I32" s="1">
         <v>5</v>
       </c>
       <c r="J32" s="4" t="s">
@@ -1062,8 +1197,11 @@
       <c r="K32" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" ht="12.8">
       <c r="B33" s="1" t="s">
         <v>62</v>
       </c>
@@ -1076,7 +1214,7 @@
       <c r="E33" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I33" s="1" t="n">
+      <c r="I33" s="1">
         <v>6</v>
       </c>
       <c r="J33" s="4" t="s">
@@ -1085,8 +1223,11 @@
       <c r="K33" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L33" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" ht="12.8">
       <c r="E34" s="1" t="s">
         <v>72</v>
       </c>
@@ -1095,38 +1236,38 @@
       </c>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="12.8">
       <c r="E35" s="1" t="s">
         <v>74</v>
       </c>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="E36" s="1" t="s">
         <v>75</v>
       </c>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.8">
       <c r="J37" s="4"/>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="12.8">
       <c r="J38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="12.8">
       <c r="A39" s="1" t="s">
         <v>54</v>
       </c>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="12.8">
       <c r="J40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="95.5">
       <c r="C41" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I41" s="1" t="n">
+      <c r="I41" s="1">
         <v>17</v>
       </c>
       <c r="J41" s="4" t="s">
@@ -1135,12 +1276,15 @@
       <c r="K41" s="4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" ht="95.5">
       <c r="C42" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I42" s="1" t="n">
+      <c r="I42" s="1">
         <v>18</v>
       </c>
       <c r="J42" s="4" t="s">
@@ -1149,12 +1293,15 @@
       <c r="K42" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L42" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" ht="85.05">
       <c r="C43" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="1" t="n">
+      <c r="I43" s="1">
         <v>19</v>
       </c>
       <c r="J43" s="4" t="s">
@@ -1163,33 +1310,36 @@
       <c r="K43" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L43" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" ht="12.8">
       <c r="B44" s="1" t="s">
         <v>82</v>
       </c>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" ht="12.8">
       <c r="J45" s="4"/>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.8">
       <c r="J46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.8">
       <c r="A47" s="1" t="s">
         <v>62</v>
       </c>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.8">
       <c r="J48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="43.25">
       <c r="C49" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I49" s="1" t="n">
+      <c r="I49" s="1">
         <v>7</v>
       </c>
       <c r="J49" s="4" t="s">
@@ -1198,12 +1348,15 @@
       <c r="K49" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L49" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50" ht="53.7">
       <c r="C50" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I50" s="1" t="n">
+      <c r="I50" s="1">
         <v>8</v>
       </c>
       <c r="J50" s="5" t="s">
@@ -1212,12 +1365,15 @@
       <c r="K50" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L50" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51" ht="43.25">
       <c r="C51" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="1" t="n">
+      <c r="I51" s="1">
         <v>9</v>
       </c>
       <c r="J51" s="4" t="s">
@@ -1226,18 +1382,21 @@
       <c r="K51" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L51" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" ht="12.8">
       <c r="J52" s="4"/>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" ht="12.8">
       <c r="B53" s="1" t="s">
         <v>89</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I53" s="1" t="n">
+      <c r="I53" s="1">
         <v>12</v>
       </c>
       <c r="J53" s="4" t="s">
@@ -1246,15 +1405,18 @@
       <c r="K53" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L53" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="54" ht="12.8">
       <c r="B54" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I54" s="1" t="n">
+      <c r="I54" s="1">
         <v>13</v>
       </c>
       <c r="J54" s="4" t="s">
@@ -1263,8 +1425,11 @@
       <c r="K54" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L54" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" ht="12.8">
       <c r="B55" s="1" t="s">
         <v>92</v>
       </c>
@@ -1273,20 +1438,20 @@
       </c>
       <c r="J55" s="4"/>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" ht="12.8">
       <c r="J56" s="4"/>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" ht="12.8">
       <c r="A57" s="1" t="s">
         <v>89</v>
       </c>
       <c r="J57" s="4"/>
     </row>
-    <row r="58" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" ht="91">
       <c r="C58" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I58" s="1" t="n">
+      <c r="I58" s="1">
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
@@ -1295,12 +1460,15 @@
       <c r="K58" s="7" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L58" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="59" ht="53.7">
       <c r="C59" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I59" s="1" t="n">
+      <c r="I59" s="1">
         <v>24</v>
       </c>
       <c r="J59" s="5" t="s">
@@ -1309,12 +1477,15 @@
       <c r="K59" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L59" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="60" ht="64.15">
       <c r="C60" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I60" s="1" t="n">
+      <c r="I60" s="1">
         <v>25</v>
       </c>
       <c r="J60" s="4" t="s">
@@ -1323,8 +1494,11 @@
       <c r="K60" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L60" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" ht="12.8">
       <c r="E61" s="1" t="s">
         <v>20</v>
       </c>
@@ -1333,25 +1507,25 @@
       </c>
       <c r="J61" s="4"/>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" ht="12.8">
       <c r="E62" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J62" s="4"/>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" ht="12.8">
       <c r="B63" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J63" s="4"/>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" ht="12.8">
       <c r="A64" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I65" s="1" t="n">
+    <row r="65" ht="12.8">
+      <c r="I65" s="1">
         <v>15</v>
       </c>
       <c r="J65" s="1" t="s">
@@ -1360,20 +1534,23 @@
       <c r="K65" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L65" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="66" ht="12.8">
       <c r="B66" s="1" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
